--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_atacama.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2023_atacama.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>29.28995121266365</v>
+      </c>
+      <c r="C2">
         <v>26.06349373486364</v>
-      </c>
-      <c r="C2">
-        <v>29.28995121266365</v>
       </c>
       <c r="D2">
         <v>3.836784163215837</v>
       </c>
       <c r="E2">
-        <v>16.77690104887403</v>
+        <v>18.85375069896694</v>
       </c>
       <c r="F2">
         <v>64.36934825215903</v>
       </c>
       <c r="G2">
-        <v>18.85375069896694</v>
+        <v>16.77690104887403</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>28.4395327691124</v>
+      </c>
+      <c r="C3">
         <v>31.78988599006784</v>
-      </c>
-      <c r="C3">
-        <v>28.4395327691124</v>
       </c>
       <c r="D3">
         <v>3.145654565456546</v>
       </c>
       <c r="E3">
-        <v>19.84023048716606</v>
+        <v>17.7492579011699</v>
       </c>
       <c r="F3">
         <v>62.41051161166405</v>
       </c>
       <c r="G3">
-        <v>17.7492579011699</v>
+        <v>19.84023048716606</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>34.31589290100712</v>
+      </c>
+      <c r="C4">
         <v>25.92729059199214</v>
-      </c>
-      <c r="C4">
-        <v>34.31589290100712</v>
       </c>
       <c r="D4">
         <v>3.856939838938891</v>
       </c>
       <c r="E4">
-        <v>16.17996474285276</v>
+        <v>21.41488464781176</v>
       </c>
       <c r="F4">
         <v>62.40515060933548</v>
       </c>
       <c r="G4">
-        <v>21.41488464781176</v>
+        <v>16.17996474285276</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>30.57240542627109</v>
+      </c>
+      <c r="C5">
         <v>33.7267012242197</v>
-      </c>
-      <c r="C5">
-        <v>30.57240542627109</v>
       </c>
       <c r="D5">
         <v>2.965009810333551</v>
       </c>
       <c r="E5">
-        <v>20.52762301134456</v>
+        <v>18.60777337719004</v>
       </c>
       <c r="F5">
-        <v>60.86460361146538</v>
+        <v>60.8646036114654</v>
       </c>
       <c r="G5">
-        <v>18.60777337719004</v>
+        <v>20.52762301134457</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>29.92242756103126</v>
+      </c>
+      <c r="C6">
         <v>24.1843486196669</v>
-      </c>
-      <c r="C6">
-        <v>29.92242756103126</v>
       </c>
       <c r="D6">
         <v>4.134905660377359</v>
       </c>
       <c r="E6">
-        <v>15.69324154267525</v>
+        <v>19.41668517284772</v>
       </c>
       <c r="F6">
         <v>64.89007328447701</v>
       </c>
       <c r="G6">
-        <v>19.41668517284773</v>
+        <v>15.69324154267525</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.74976070012307</v>
+      </c>
+      <c r="C7">
         <v>33.63052099001778</v>
-      </c>
-      <c r="C7">
-        <v>29.74976070012307</v>
       </c>
       <c r="D7">
         <v>2.973489468976173</v>
       </c>
       <c r="E7">
-        <v>20.58419819216606</v>
+        <v>18.20890525610981</v>
       </c>
       <c r="F7">
         <v>61.20689655172414</v>
       </c>
       <c r="G7">
-        <v>18.20890525610981</v>
+        <v>20.58419819216606</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>29.03973509933775</v>
+      </c>
+      <c r="C8">
         <v>44.03973509933775</v>
-      </c>
-      <c r="C8">
-        <v>29.03973509933775</v>
       </c>
       <c r="D8">
         <v>2.270676691729324</v>
       </c>
       <c r="E8">
-        <v>25.44480581595561</v>
+        <v>16.77826669217524</v>
       </c>
       <c r="F8">
         <v>57.77692749186915</v>
       </c>
       <c r="G8">
-        <v>16.77826669217524</v>
+        <v>25.44480581595561</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>30.67484662576687</v>
+      </c>
+      <c r="C9">
         <v>36.05778745299822</v>
-      </c>
-      <c r="C9">
-        <v>30.67484662576687</v>
       </c>
       <c r="D9">
         <v>2.773326015367728</v>
       </c>
       <c r="E9">
-        <v>21.62611275964392</v>
+        <v>18.39762611275965</v>
       </c>
       <c r="F9">
         <v>59.97626112759644</v>
       </c>
       <c r="G9">
-        <v>18.39762611275965</v>
+        <v>21.62611275964392</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>29.03225806451613</v>
+      </c>
+      <c r="C10">
         <v>36.06220280169644</v>
-      </c>
-      <c r="C10">
-        <v>29.03225806451613</v>
       </c>
       <c r="D10">
         <v>2.772986457590877</v>
       </c>
       <c r="E10">
+        <v>17.5852405418029</v>
+      </c>
+      <c r="F10">
+        <v>60.5713840884322</v>
+      </c>
+      <c r="G10">
         <v>21.84337536976491</v>
-      </c>
-      <c r="F10">
-        <v>60.57138408843219</v>
-      </c>
-      <c r="G10">
-        <v>17.5852405418029</v>
       </c>
     </row>
   </sheetData>
